--- a/data/trans_dic/P1423-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1423-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad) (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,42 +717,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,01</t>
+          <t>0,23; 2,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,69</t>
+          <t>0,24; 2,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,96</t>
+          <t>0,77; 6,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,38</t>
+          <t>1,41; 4,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,25</t>
+          <t>0,61; 3,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,46</t>
+          <t>1,53; 5,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 10,94</t>
+          <t>2,98; 11,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,2</t>
+          <t>0,55; 2,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,16</t>
+          <t>1,22; 3,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,57</t>
+          <t>2,19; 6,39</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,98</t>
+          <t>1,12; 3,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,54</t>
+          <t>1,89; 4,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,5</t>
+          <t>0,5; 2,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,87</t>
+          <t>1,23; 4,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,3</t>
+          <t>2,28; 5,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,39</t>
+          <t>2,75; 6,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,97</t>
+          <t>1,35; 3,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 9,16</t>
+          <t>3,91; 9,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 3,6</t>
+          <t>1,85; 3,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,92</t>
+          <t>2,69; 5,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,62</t>
+          <t>1,16; 2,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,51</t>
+          <t>3,27; 6,67</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,58</t>
+          <t>1,81; 4,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,73</t>
+          <t>2,47; 5,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,06</t>
+          <t>1,4; 4,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,14; 8,26</t>
+          <t>4,08; 8,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 7,8</t>
+          <t>4,22; 7,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,65; 12,1</t>
+          <t>7,73; 12,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,72</t>
+          <t>4,99; 8,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 9,37</t>
+          <t>5,18; 9,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,71</t>
+          <t>3,37; 5,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 8,27</t>
+          <t>5,6; 8,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 5,79</t>
+          <t>3,61; 5,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 8,07</t>
+          <t>5,23; 8,2</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,97</t>
+          <t>1,81; 4,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,55</t>
+          <t>2,95; 6,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,95</t>
+          <t>2,71; 5,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 8,58</t>
+          <t>2,36; 8,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 13,99</t>
+          <t>8,61; 14,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 15,61</t>
+          <t>9,89; 15,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,16; 14,62</t>
+          <t>9,57; 14,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,21; 14,7</t>
+          <t>10,29; 14,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,61; 8,75</t>
+          <t>5,66; 8,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 10,45</t>
+          <t>7,0; 10,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 9,65</t>
+          <t>6,41; 9,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 10,77</t>
+          <t>5,39; 10,99</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 8,06</t>
+          <t>3,59; 8,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,22; 10,12</t>
+          <t>4,98; 10,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 9,47</t>
+          <t>4,55; 9,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,51; 12,24</t>
+          <t>7,39; 11,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,64; 16,68</t>
+          <t>9,62; 16,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,73; 22,54</t>
+          <t>14,96; 22,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,52; 21,71</t>
+          <t>14,63; 21,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,07; 19,78</t>
+          <t>15,27; 20,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,49; 11,51</t>
+          <t>7,45; 11,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,81; 15,45</t>
+          <t>10,84; 15,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,03; 14,43</t>
+          <t>10,23; 14,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,81; 15,11</t>
+          <t>11,9; 15,24</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,2; 8,05</t>
+          <t>3,18; 7,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,98; 8,85</t>
+          <t>3,02; 8,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,16</t>
+          <t>1,43; 5,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,78</t>
+          <t>3,18; 6,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,7; 15,15</t>
+          <t>8,73; 15,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,5; 23,69</t>
+          <t>15,47; 24,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,72; 21,34</t>
+          <t>13,35; 21,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,26; 16,48</t>
+          <t>4,5; 16,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,85; 11,08</t>
+          <t>6,86; 10,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,15; 15,63</t>
+          <t>10,34; 15,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,5; 13,38</t>
+          <t>8,43; 13,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,43; 11,16</t>
+          <t>4,09; 11,06</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,29; 10,87</t>
+          <t>4,16; 11,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,79; 11,16</t>
+          <t>3,77; 11,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,79; 9,12</t>
+          <t>3,79; 9,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,59; 12,24</t>
+          <t>6,61; 11,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,85; 13,61</t>
+          <t>6,73; 13,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,93; 23,54</t>
+          <t>14,74; 23,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,46; 19,68</t>
+          <t>11,19; 19,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,59; 18,83</t>
+          <t>13,83; 18,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,43; 11,52</t>
+          <t>6,5; 11,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,45; 17,37</t>
+          <t>11,65; 17,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,1; 14,43</t>
+          <t>9,19; 14,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,61; 15,56</t>
+          <t>11,63; 15,15</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,7</t>
+          <t>2,52; 3,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,48; 4,95</t>
+          <t>3,47; 4,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,93</t>
+          <t>2,69; 3,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,7</t>
+          <t>4,5; 6,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,71; 8,54</t>
+          <t>6,72; 8,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,24; 12,41</t>
+          <t>10,32; 12,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,24; 11,27</t>
+          <t>9,13; 11,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,97; 12,34</t>
+          <t>9,01; 12,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,88; 5,99</t>
+          <t>4,91; 5,96</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,23; 8,59</t>
+          <t>7,26; 8,56</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,14; 7,43</t>
+          <t>6,26; 7,49</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,44; 9,39</t>
+          <t>7,33; 9,33</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad) (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4750</t>
+          <t>0; 4843</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>993; 9110</t>
+          <t>1042; 9227</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1060; 11298</t>
+          <t>989; 9689</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2745; 23844</t>
+          <t>3078; 27427</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6476; 20488</t>
+          <t>6595; 21283</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2686; 13982</t>
+          <t>2628; 13645</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6635; 21620</t>
+          <t>6070; 21771</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10252; 34275</t>
+          <t>9334; 34990</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6996; 20646</t>
+          <t>7039; 20630</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5129; 19412</t>
+          <t>4844; 18885</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9471; 25779</t>
+          <t>9930; 26276</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16354; 46821</t>
+          <t>15617; 45574</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8327; 21948</t>
+          <t>8239; 23623</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12790; 31168</t>
+          <t>12988; 32654</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2988; 14783</t>
+          <t>2968; 13150</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4885; 20615</t>
+          <t>5202; 20876</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14328; 33165</t>
+          <t>14281; 33744</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17229; 38992</t>
+          <t>16792; 37911</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7782; 22364</t>
+          <t>7632; 21622</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18820; 46930</t>
+          <t>20002; 47954</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26272; 48947</t>
+          <t>25148; 48590</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33645; 63834</t>
+          <t>34885; 66123</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13395; 30201</t>
+          <t>13354; 30821</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29643; 60871</t>
+          <t>30617; 62387</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11753; 29229</t>
+          <t>11567; 30297</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16634; 39068</t>
+          <t>16867; 39734</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10154; 27141</t>
+          <t>9336; 27000</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22181; 44323</t>
+          <t>21896; 44443</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28810; 53826</t>
+          <t>29083; 53292</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54250; 85886</t>
+          <t>54844; 87019</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33007; 57642</t>
+          <t>33024; 59098</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31370; 55489</t>
+          <t>30667; 54696</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45629; 75833</t>
+          <t>44772; 75505</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76207; 115035</t>
+          <t>77911; 117054</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47381; 77030</t>
+          <t>48089; 75650</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58916; 91045</t>
+          <t>58973; 92559</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9261; 25782</t>
+          <t>9418; 25516</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18408; 40273</t>
+          <t>18127; 39151</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17592; 38454</t>
+          <t>17528; 37835</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20226; 76148</t>
+          <t>20928; 74368</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44700; 72162</t>
+          <t>44383; 73506</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61625; 95887</t>
+          <t>60753; 95672</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59434; 94918</t>
+          <t>62090; 95959</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>72808; 104763</t>
+          <t>73368; 104961</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58081; 90540</t>
+          <t>58567; 91602</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>84457; 128428</t>
+          <t>85980; 123683</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85023; 124966</t>
+          <t>83025; 123174</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>80129; 172457</t>
+          <t>86257; 175844</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14013; 31153</t>
+          <t>13871; 31226</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22420; 43451</t>
+          <t>21369; 43429</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21589; 45266</t>
+          <t>21736; 47509</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42138; 68721</t>
+          <t>41467; 65389</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38961; 67399</t>
+          <t>38868; 65658</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>65953; 100921</t>
+          <t>66996; 100684</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>72158; 107861</t>
+          <t>72699; 107773</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>82553; 108383</t>
+          <t>83639; 110413</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59257; 91011</t>
+          <t>58930; 91181</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>94803; 135555</t>
+          <t>95116; 134531</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>97815; 140652</t>
+          <t>99738; 141926</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>130981; 167623</t>
+          <t>131975; 168994</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9354; 23549</t>
+          <t>9290; 23010</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9241; 27402</t>
+          <t>9365; 27350</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4813; 17236</t>
+          <t>4795; 16851</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11510; 24961</t>
+          <t>11698; 25119</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29828; 51965</t>
+          <t>29941; 52601</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54865; 83874</t>
+          <t>54757; 84945</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51829; 80630</t>
+          <t>50433; 81117</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>25898; 100270</t>
+          <t>27367; 101406</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>43507; 70403</t>
+          <t>43568; 69468</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>67372; 103751</t>
+          <t>68654; 103151</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>60520; 95285</t>
+          <t>60000; 94022</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>43220; 109018</t>
+          <t>39901; 108036</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8996; 22815</t>
+          <t>8731; 23609</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9477; 27877</t>
+          <t>9410; 28399</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9740; 23430</t>
+          <t>9739; 23761</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18642; 34608</t>
+          <t>18697; 33624</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22887; 45431</t>
+          <t>22456; 45425</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>58082; 91566</t>
+          <t>57349; 90094</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45842; 78734</t>
+          <t>44764; 77140</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>57855; 80170</t>
+          <t>58909; 80810</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>34958; 62656</t>
+          <t>35369; 63437</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>73115; 110959</t>
+          <t>74420; 111809</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59821; 94854</t>
+          <t>60377; 95513</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>82276; 110247</t>
+          <t>82434; 107370</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>82495; 121211</t>
+          <t>82672; 122507</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>119409; 169596</t>
+          <t>118968; 168850</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>92138; 133487</t>
+          <t>91379; 132771</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>156248; 231927</t>
+          <t>155788; 229127</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>226831; 288464</t>
+          <t>226997; 288276</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>364180; 441185</t>
+          <t>366728; 444837</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>327383; 399455</t>
+          <t>323651; 398752</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>333079; 458157</t>
+          <t>334413; 455450</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>324573; 398476</t>
+          <t>326547; 396959</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>504880; 599533</t>
+          <t>506773; 597587</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>425952; 515234</t>
+          <t>434571; 519549</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>533889; 673135</t>
+          <t>525435; 669137</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1423-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1423-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,03</t>
+          <t>0,23; 2,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,31</t>
+          <t>0,34; 2,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,86</t>
+          <t>0,83; 5,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,55</t>
+          <t>1,36; 4,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,17</t>
+          <t>0,64; 3,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,5</t>
+          <t>1,64; 5,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 11,17</t>
+          <t>2,94; 9,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,15</t>
+          <t>0,69; 2,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,14</t>
+          <t>0,63; 2,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,22</t>
+          <t>1,17; 3,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,39</t>
+          <t>2,29; 6,17</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,21</t>
+          <t>1,06; 3,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,75</t>
+          <t>1,72; 4,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,23</t>
+          <t>0,5; 2,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,93</t>
+          <t>1,68; 5,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,39</t>
+          <t>2,24; 5,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,21</t>
+          <t>2,84; 6,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,84</t>
+          <t>1,34; 3,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 9,36</t>
+          <t>5,07; 10,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,57</t>
+          <t>1,87; 3,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,1</t>
+          <t>2,68; 4,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,67</t>
+          <t>1,17; 2,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,67</t>
+          <t>3,67; 6,81</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,74</t>
+          <t>1,77; 4,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,83</t>
+          <t>2,42; 5,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,04</t>
+          <t>1,38; 3,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,29</t>
+          <t>3,76; 7,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 7,73</t>
+          <t>4,09; 7,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,26</t>
+          <t>7,72; 12,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,94</t>
+          <t>5,28; 8,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 9,24</t>
+          <t>6,25; 9,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,68</t>
+          <t>3,39; 5,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 8,41</t>
+          <t>5,59; 8,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,69</t>
+          <t>3,49; 5,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,2</t>
+          <t>5,49; 8,08</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,92</t>
+          <t>1,7; 4,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,37</t>
+          <t>3,07; 6,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,86</t>
+          <t>2,66; 5,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 8,38</t>
+          <t>5,94; 10,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 14,26</t>
+          <t>8,67; 14,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,89; 15,58</t>
+          <t>9,89; 15,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,57; 14,78</t>
+          <t>9,43; 14,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,29; 14,72</t>
+          <t>11,3; 15,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,85</t>
+          <t>5,62; 8,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,0; 10,06</t>
+          <t>6,86; 10,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,41; 9,51</t>
+          <t>6,35; 9,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,39; 10,99</t>
+          <t>9,29; 12,25</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 8,07</t>
+          <t>3,74; 8,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,98; 10,11</t>
+          <t>4,8; 10,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 9,94</t>
+          <t>4,49; 9,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 11,65</t>
+          <t>7,11; 11,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,62; 16,25</t>
+          <t>9,74; 16,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,96; 22,48</t>
+          <t>14,94; 22,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,63; 21,69</t>
+          <t>14,24; 20,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,27; 20,15</t>
+          <t>15,1; 19,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,45; 11,53</t>
+          <t>7,44; 11,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,84; 15,34</t>
+          <t>10,75; 15,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,23; 14,56</t>
+          <t>10,28; 14,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,9; 15,24</t>
+          <t>11,81; 15,13</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,18; 7,86</t>
+          <t>2,99; 7,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,02; 8,83</t>
+          <t>2,92; 8,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,04</t>
+          <t>1,42; 5,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,82</t>
+          <t>3,01; 6,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,73; 15,34</t>
+          <t>8,81; 15,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,47; 24,0</t>
+          <t>15,48; 24,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,35; 21,47</t>
+          <t>13,6; 21,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,5; 16,67</t>
+          <t>13,5; 18,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,86; 10,93</t>
+          <t>6,9; 11,24</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,34; 15,54</t>
+          <t>10,34; 15,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,43; 13,2</t>
+          <t>8,28; 13,1</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,09; 11,06</t>
+          <t>8,83; 11,92</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 11,25</t>
+          <t>3,99; 10,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,77; 11,37</t>
+          <t>3,95; 11,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,79; 9,25</t>
+          <t>3,84; 8,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,61; 11,89</t>
+          <t>6,64; 11,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,73; 13,6</t>
+          <t>6,6; 13,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,74; 23,16</t>
+          <t>15,24; 23,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,19; 19,28</t>
+          <t>11,19; 19,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,83; 18,98</t>
+          <t>13,89; 19,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,5; 11,67</t>
+          <t>6,41; 11,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,65; 17,5</t>
+          <t>11,5; 17,34</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,19; 14,53</t>
+          <t>9,12; 14,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,63; 15,15</t>
+          <t>11,67; 15,62</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,74</t>
+          <t>2,54; 3,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,93</t>
+          <t>3,43; 4,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,69; 3,91</t>
+          <t>2,71; 3,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,62</t>
+          <t>5,29; 7,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,72; 8,53</t>
+          <t>6,57; 8,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,32; 12,51</t>
+          <t>10,44; 12,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,13; 11,25</t>
+          <t>9,12; 11,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,01; 12,27</t>
+          <t>11,32; 13,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,91; 5,96</t>
+          <t>4,78; 5,92</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,26; 8,56</t>
+          <t>7,23; 8,51</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,49</t>
+          <t>6,26; 7,51</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,33; 9,33</t>
+          <t>8,54; 9,81</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19579</t>
+          <t>20141</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28498</t>
+          <t>30449</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4843</t>
+          <t>0; 5797</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1042; 9227</t>
+          <t>1028; 9985</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>989; 9689</t>
+          <t>1408; 10928</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3078; 27427</t>
+          <t>3390; 22387</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6595; 21283</t>
+          <t>6369; 19985</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2628; 13645</t>
+          <t>2769; 14277</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6070; 21771</t>
+          <t>6480; 20831</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9334; 34990</t>
+          <t>10668; 34576</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7039; 20630</t>
+          <t>6612; 21669</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4844; 18885</t>
+          <t>5580; 18204</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9930; 26276</t>
+          <t>9573; 26432</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15617; 45574</t>
+          <t>17665; 47512</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>14565</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33339</t>
+          <t>35832</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>44112</t>
+          <t>50397</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8239; 23623</t>
+          <t>7785; 22365</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12988; 32654</t>
+          <t>11833; 32260</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2968; 13150</t>
+          <t>2963; 13082</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5202; 20876</t>
+          <t>8013; 27077</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14281; 33744</t>
+          <t>14007; 33438</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16792; 37911</t>
+          <t>17318; 38189</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7632; 21622</t>
+          <t>7546; 22343</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20002; 47954</t>
+          <t>25421; 52342</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25148; 48590</t>
+          <t>25486; 49432</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34885; 66123</t>
+          <t>34720; 63824</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13354; 30821</t>
+          <t>13521; 30244</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30617; 62387</t>
+          <t>35944; 66634</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31742</t>
+          <t>33653</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>49394</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74207</t>
+          <t>83048</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11567; 30297</t>
+          <t>11295; 28039</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16867; 39734</t>
+          <t>16516; 40123</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9336; 27000</t>
+          <t>9244; 25432</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21896; 44443</t>
+          <t>23321; 49144</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29083; 53292</t>
+          <t>28203; 54635</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54844; 87019</t>
+          <t>54779; 87397</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33024; 59098</t>
+          <t>34898; 58497</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30667; 54696</t>
+          <t>38923; 60501</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44772; 75505</t>
+          <t>45089; 75407</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77911; 117054</t>
+          <t>77717; 117654</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48089; 75650</t>
+          <t>46500; 76617</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58973; 92559</t>
+          <t>68247; 100511</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49301</t>
+          <t>54405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>89648</t>
+          <t>98542</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>138949</t>
+          <t>152947</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9418; 25516</t>
+          <t>8817; 24686</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18127; 39151</t>
+          <t>18881; 39955</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17528; 37835</t>
+          <t>17163; 37719</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20928; 74368</t>
+          <t>41622; 72151</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44383; 73506</t>
+          <t>44702; 72776</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60753; 95672</t>
+          <t>60765; 94827</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62090; 95959</t>
+          <t>61214; 96241</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>73368; 104961</t>
+          <t>83304; 112381</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58567; 91602</t>
+          <t>58185; 90571</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>85980; 123683</t>
+          <t>84345; 125176</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83025; 123174</t>
+          <t>82256; 123418</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>86257; 175844</t>
+          <t>133527; 176109</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53801</t>
+          <t>55744</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>96299</t>
+          <t>107090</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>150100</t>
+          <t>162834</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13871; 31226</t>
+          <t>14477; 32172</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21369; 43429</t>
+          <t>20592; 43119</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21736; 47509</t>
+          <t>21479; 44149</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41467; 65389</t>
+          <t>43310; 71256</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38868; 65658</t>
+          <t>39334; 66880</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66996; 100684</t>
+          <t>66908; 101103</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>72699; 107773</t>
+          <t>70774; 104083</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>83639; 110413</t>
+          <t>91910; 120463</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>58930; 91181</t>
+          <t>58853; 90867</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>95116; 134531</t>
+          <t>94320; 134673</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99738; 141926</t>
+          <t>100181; 143959</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>131975; 168994</t>
+          <t>143916; 184364</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>18351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>62958</t>
+          <t>69348</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>80417</t>
+          <t>87699</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9290; 23010</t>
+          <t>8750; 23082</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9365; 27350</t>
+          <t>9044; 27795</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4795; 16851</t>
+          <t>4764; 16842</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11698; 25119</t>
+          <t>12251; 26566</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29941; 52601</t>
+          <t>30211; 53175</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54757; 84945</t>
+          <t>54803; 85413</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50433; 81117</t>
+          <t>51391; 81366</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27367; 101406</t>
+          <t>59292; 81689</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>43568; 69468</t>
+          <t>43866; 71430</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68654; 103151</t>
+          <t>68634; 105472</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>60000; 94022</t>
+          <t>58990; 93299</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>39901; 108036</t>
+          <t>74744; 100898</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>28022</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>68840</t>
+          <t>76283</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94212</t>
+          <t>104304</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8731; 23609</t>
+          <t>8377; 23062</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9410; 28399</t>
+          <t>9857; 29780</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9739; 23761</t>
+          <t>9863; 22752</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18697; 33624</t>
+          <t>20592; 37030</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22456; 45425</t>
+          <t>22038; 45884</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>57349; 90094</t>
+          <t>59278; 90566</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44764; 77140</t>
+          <t>44785; 77118</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>58909; 80810</t>
+          <t>64524; 88498</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>35369; 63437</t>
+          <t>34867; 63509</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>74420; 111809</t>
+          <t>73441; 110748</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>60377; 95513</t>
+          <t>59939; 94640</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>82434; 107370</t>
+          <t>90391; 120996</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>197367</t>
+          <t>215047</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>413127</t>
+          <t>456631</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>610494</t>
+          <t>671678</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>82672; 122507</t>
+          <t>83266; 121468</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>118968; 168850</t>
+          <t>117403; 170544</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>91379; 132771</t>
+          <t>91904; 132452</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>155788; 229127</t>
+          <t>186900; 247797</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>226997; 288276</t>
+          <t>222029; 284522</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>366728; 444837</t>
+          <t>371315; 444017</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>323651; 398752</t>
+          <t>323335; 399186</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>334413; 455450</t>
+          <t>422986; 493459</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>326547; 396959</t>
+          <t>318267; 393864</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>506773; 597587</t>
+          <t>504603; 594476</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>434571; 519549</t>
+          <t>434479; 521099</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>525435; 669137</t>
+          <t>620917; 712908</t>
         </is>
       </c>
     </row>
